--- a/data/Pokerbilanz.xlsx
+++ b/data/Pokerbilanz.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3986C3747C471C36/Dokumente/Coding Projekte/PokerDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{E4E725D7-5AF4-4991-BA9C-4F7D82DBD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6921E69B-D831-4692-82E5-BE92F3EE3184}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{E4E725D7-5AF4-4991-BA9C-4F7D82DBD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EC76B0E-CB8E-426C-8ED2-B65EB63AD169}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="380">
   <si>
     <t>Julius</t>
   </si>
@@ -1175,6 +1175,9 @@
   </si>
   <si>
     <t>14.08.2026</t>
+  </si>
+  <si>
+    <t>11.09.2026</t>
   </si>
 </sst>
 </file>
@@ -6823,7 +6826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ207"/>
+  <dimension ref="A1:AZ208"/>
   <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.3">
@@ -20298,7 +20301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B193">
         <v>-37.299999999999997</v>
       </c>
@@ -20325,7 +20328,7 @@
         <v>-9.9999999999994316E-2</v>
       </c>
     </row>
-    <row r="194" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B194" s="2">
         <v>8.3000000000000007</v>
       </c>
@@ -20351,11 +20354,11 @@
         <v>363</v>
       </c>
       <c r="AZ194">
-        <f t="shared" ref="AZ194:AZ207" si="0">SUM(A194:AX194)</f>
+        <f t="shared" ref="AZ194:AZ208" si="0">SUM(A194:AX194)</f>
         <v>5.0000000000004263E-2</v>
       </c>
     </row>
-    <row r="195" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B195" s="2">
         <v>42.1</v>
       </c>
@@ -20379,7 +20382,7 @@
         <v>0.10000000000000853</v>
       </c>
     </row>
-    <row r="196" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B196" s="2">
         <v>-30</v>
       </c>
@@ -20406,7 +20409,7 @@
         <v>2.0000000000000009</v>
       </c>
     </row>
-    <row r="197" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B197" s="2">
         <v>-70</v>
       </c>
@@ -20433,7 +20436,7 @@
         <v>2.4999999999999929</v>
       </c>
     </row>
-    <row r="198" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B198" s="2">
         <v>12.4</v>
       </c>
@@ -20457,7 +20460,7 @@
         <v>-2.9999999999999929</v>
       </c>
     </row>
-    <row r="199" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B199" s="2">
         <v>-80</v>
       </c>
@@ -20496,7 +20499,7 @@
         <v>1.1999999999999957</v>
       </c>
     </row>
-    <row r="200" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B200" s="2">
         <v>26.1</v>
       </c>
@@ -20523,7 +20526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B201" s="2">
         <v>5</v>
       </c>
@@ -20547,7 +20550,7 @@
         <v>-0.20000000000000284</v>
       </c>
     </row>
-    <row r="202" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B202" s="2">
         <v>54.5</v>
       </c>
@@ -20574,7 +20577,7 @@
         <v>-9.9999999999994316E-2</v>
       </c>
     </row>
-    <row r="203" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B203" s="2">
         <v>-20</v>
       </c>
@@ -20607,7 +20610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:52" x14ac:dyDescent="0.3">
       <c r="C204" s="2">
         <v>-50</v>
       </c>
@@ -20631,7 +20634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B205" s="2">
         <v>24.3</v>
       </c>
@@ -20664,7 +20667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B206" s="2">
         <v>-23.8</v>
       </c>
@@ -20691,7 +20694,7 @@
         <v>1.8999999999999915</v>
       </c>
     </row>
-    <row r="207" spans="2:52" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:52" x14ac:dyDescent="0.3">
       <c r="B207" s="2">
         <v>47.2</v>
       </c>
@@ -20716,6 +20719,33 @@
       <c r="AZ207">
         <f t="shared" si="0"/>
         <v>1.4000000000000021</v>
+      </c>
+    </row>
+    <row r="208" spans="1:52" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>-10</v>
+      </c>
+      <c r="B208" s="2">
+        <v>12.2</v>
+      </c>
+      <c r="C208" s="2">
+        <v>16.3</v>
+      </c>
+      <c r="L208">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AE208">
+        <v>-40</v>
+      </c>
+      <c r="AM208">
+        <v>20.2</v>
+      </c>
+      <c r="AY208" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="AZ208">
+        <f t="shared" si="0"/>
+        <v>-0.19999999999999929</v>
       </c>
     </row>
   </sheetData>

--- a/data/Pokerbilanz.xlsx
+++ b/data/Pokerbilanz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3986C3747C471C36/Dokumente/Coding Projekte/PokerDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{E4E725D7-5AF4-4991-BA9C-4F7D82DBD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EC76B0E-CB8E-426C-8ED2-B65EB63AD169}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="13_ncr:1_{E4E725D7-5AF4-4991-BA9C-4F7D82DBD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56B7E6F0-33F4-4015-A226-F7A815F50B46}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="381">
   <si>
     <t>Julius</t>
   </si>
@@ -1178,6 +1178,9 @@
   </si>
   <si>
     <t>11.09.2026</t>
+  </si>
+  <si>
+    <t>18.09.2026</t>
   </si>
 </sst>
 </file>
@@ -6826,7 +6829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ208"/>
+  <dimension ref="A1:AZ209"/>
   <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.3">
@@ -20354,7 +20357,7 @@
         <v>363</v>
       </c>
       <c r="AZ194">
-        <f t="shared" ref="AZ194:AZ208" si="0">SUM(A194:AX194)</f>
+        <f t="shared" ref="AZ194:AZ209" si="0">SUM(A194:AX194)</f>
         <v>5.0000000000004263E-2</v>
       </c>
     </row>
@@ -20746,6 +20749,33 @@
       <c r="AZ208">
         <f t="shared" si="0"/>
         <v>-0.19999999999999929</v>
+      </c>
+    </row>
+    <row r="209" spans="2:52" x14ac:dyDescent="0.3">
+      <c r="B209" s="2">
+        <v>-29.8</v>
+      </c>
+      <c r="C209" s="2">
+        <v>68</v>
+      </c>
+      <c r="D209">
+        <v>22</v>
+      </c>
+      <c r="L209">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="T209" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="AM209">
+        <v>-58.8</v>
+      </c>
+      <c r="AY209" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="AZ209">
+        <f t="shared" si="0"/>
+        <v>-0.69999999999999574</v>
       </c>
     </row>
   </sheetData>

--- a/data/Pokerbilanz.xlsx
+++ b/data/Pokerbilanz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3986C3747C471C36/Dokumente/Coding Projekte/PokerDashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="13_ncr:1_{E4E725D7-5AF4-4991-BA9C-4F7D82DBD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56B7E6F0-33F4-4015-A226-F7A815F50B46}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{E4E725D7-5AF4-4991-BA9C-4F7D82DBD139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4A578BA-28CB-4984-AD7B-3DFC37434470}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="382">
   <si>
     <t>Julius</t>
   </si>
@@ -1181,6 +1181,9 @@
   </si>
   <si>
     <t>18.09.2026</t>
+  </si>
+  <si>
+    <t>25.09.2026</t>
   </si>
 </sst>
 </file>
@@ -6829,7 +6832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ209"/>
+  <dimension ref="A1:AZ210"/>
   <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.3">
@@ -20357,7 +20360,7 @@
         <v>363</v>
       </c>
       <c r="AZ194">
-        <f t="shared" ref="AZ194:AZ209" si="0">SUM(A194:AX194)</f>
+        <f t="shared" ref="AZ194:AZ210" si="0">SUM(A194:AX194)</f>
         <v>5.0000000000004263E-2</v>
       </c>
     </row>
@@ -20776,6 +20779,30 @@
       <c r="AZ209">
         <f t="shared" si="0"/>
         <v>-0.69999999999999574</v>
+      </c>
+    </row>
+    <row r="210" spans="2:52" x14ac:dyDescent="0.3">
+      <c r="B210" s="2">
+        <v>-50</v>
+      </c>
+      <c r="C210" s="2">
+        <v>-30</v>
+      </c>
+      <c r="L210">
+        <v>17.7</v>
+      </c>
+      <c r="T210" s="2">
+        <v>25</v>
+      </c>
+      <c r="AX210">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="AY210" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="AZ210">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
